--- a/ttl_long/AdHoc_Net_13.xlsx
+++ b/ttl_long/AdHoc_Net_13.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>84</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>59</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>305</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>128</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>278</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>157</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>83</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>152</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>97</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>163</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>237</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>309</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>108</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>372</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>319</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>471</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>279</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>438</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>382</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>556</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>219</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>480</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>502</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>604</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>182</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>605</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>305</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>618</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>749</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>233</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>708</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>345</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>740</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>899</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>803</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>336</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>826</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>951</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>199</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>881</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>275</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>960</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1008</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>118</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>990</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>345</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1020</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1165</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>194</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1152</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>280</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1129</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1282</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>197</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1306</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>290</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1236</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>113</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1385</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>171</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1410</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1329</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1446</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>112</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1498</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>298</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1466</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1617</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,46 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>156</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1519</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1689</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D139"/>
+  <dimension ref="A1:D154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1278,7 +1312,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1300,7 +1334,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1322,7 +1356,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1344,7 +1378,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1366,7 +1400,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1388,7 +1422,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1410,7 +1444,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1427,12 +1461,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1454,7 +1488,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1476,7 +1510,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1493,7 +1527,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1515,12 +1549,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1542,7 +1576,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1564,7 +1598,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1581,12 +1615,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1608,7 +1642,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1630,7 +1664,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1647,12 +1681,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1674,7 +1708,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1691,12 +1725,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1713,12 +1747,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1740,7 +1774,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1757,12 +1791,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1779,12 +1813,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1801,12 +1835,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1823,12 +1857,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1845,7 +1879,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1867,7 +1901,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1889,12 +1923,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1911,12 +1945,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1933,12 +1967,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1955,12 +1989,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1977,12 +2011,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1999,12 +2033,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2021,12 +2055,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2043,12 +2077,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2065,12 +2099,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2087,12 +2121,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2109,12 +2143,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2131,12 +2165,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2153,12 +2187,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2175,12 +2209,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2197,12 +2231,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2219,12 +2253,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2241,12 +2275,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2263,12 +2297,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2285,12 +2319,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2307,12 +2341,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2334,7 +2368,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2351,12 +2385,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2378,7 +2412,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2395,12 +2429,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2417,12 +2451,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2461,12 +2495,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2483,12 +2517,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2505,12 +2539,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2532,7 +2566,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2549,12 +2583,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2571,12 +2605,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2598,7 +2632,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2615,12 +2649,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2637,12 +2671,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2659,12 +2693,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2686,7 +2720,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2703,7 +2737,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2725,12 +2759,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2747,12 +2781,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2774,7 +2808,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2791,12 +2825,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2813,7 +2847,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2835,12 +2869,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2857,12 +2891,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2879,12 +2913,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2901,12 +2935,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2923,12 +2957,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2945,12 +2979,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2967,12 +3001,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2989,12 +3023,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3011,12 +3045,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3033,12 +3067,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3055,12 +3089,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3077,12 +3111,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3099,12 +3133,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3121,12 +3155,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3143,12 +3177,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3165,12 +3199,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3187,12 +3221,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3209,12 +3243,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3236,7 +3270,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3258,7 +3292,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3280,7 +3314,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3302,7 +3336,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3341,12 +3375,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3368,7 +3402,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3390,7 +3424,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3412,7 +3446,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3434,7 +3468,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3456,7 +3490,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3478,7 +3512,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3544,7 +3578,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3566,7 +3600,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3583,12 +3617,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3605,12 +3639,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3632,7 +3666,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3649,12 +3683,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3671,12 +3705,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3698,7 +3732,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3715,12 +3749,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3737,12 +3771,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3759,12 +3793,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3781,12 +3815,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3803,12 +3837,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3825,12 +3859,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3847,12 +3881,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3869,12 +3903,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3891,12 +3925,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3913,12 +3947,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3935,12 +3969,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3957,12 +3991,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3979,12 +4013,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4001,12 +4035,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4023,12 +4057,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4045,12 +4079,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4067,12 +4101,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4089,12 +4123,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4111,12 +4145,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4133,12 +4167,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4155,7 +4189,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4177,12 +4211,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4199,12 +4233,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4221,12 +4255,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4243,7 +4277,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4265,12 +4299,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4287,20 +4321,350 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -4349,7 +4713,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -4375,7 +4739,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_13.xlsx
+++ b/ttl_long/AdHoc_Net_13.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>74</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>52</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>218</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>85</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>303</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>110</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>102</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>351</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>189</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>278</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>182</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>298</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>214</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>382</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>363</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>324</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>366</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>463</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>244</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>469</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>519</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>691</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>142</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>705</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>284</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>580</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>671</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>181</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>732</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>389</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>746</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>944</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>828</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>328</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>875</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>968</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>117</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>1025</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>990</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>84</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>1140</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>212</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>1115</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>1125</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1324</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>282</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1244</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>302</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1275</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1401</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1286</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>390</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1403</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1420</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>246</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1520</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>283</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1451</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1567</t>
         </is>
       </c>
     </row>
@@ -1123,148 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1410</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1329</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1446</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1498</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1466</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1617</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1689</t>
+          <t>1653</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1312,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1334,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1356,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1378,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1400,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1422,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1444,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1461,12 +1325,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1488,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1527,12 +1391,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1576,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1598,7 +1462,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1615,12 +1479,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1642,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1664,7 +1528,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1681,12 +1545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1703,12 +1567,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1725,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1747,12 +1611,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1774,7 +1638,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1791,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1813,12 +1677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1835,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1857,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1879,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1901,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1923,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1945,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1967,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1989,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2011,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2033,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2055,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2077,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2099,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2121,12 +1985,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2143,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2165,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2187,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2209,7 +2073,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2231,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2258,7 +2122,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2280,7 +2144,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2297,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2346,7 +2210,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2368,7 +2232,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2390,7 +2254,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2412,7 +2276,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2429,7 +2293,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2451,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2478,7 +2342,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2495,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2522,7 +2386,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2544,7 +2408,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2566,7 +2430,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2588,7 +2452,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2605,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2627,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2649,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2671,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2698,7 +2562,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2720,7 +2584,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2737,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2759,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2786,7 +2650,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2803,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2830,7 +2694,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2847,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2874,7 +2738,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2913,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2940,7 +2804,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2957,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2979,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3006,7 +2870,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3023,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3045,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3072,7 +2936,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3089,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3111,12 +2975,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3138,7 +3002,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3155,12 +3019,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3177,7 +3041,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3199,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3221,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3243,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3265,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3287,12 +3151,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3309,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3331,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3353,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3375,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3397,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3419,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3441,7 +3305,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3463,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3485,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3507,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3529,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3551,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3595,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3617,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3639,12 +3503,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3661,12 +3525,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3683,12 +3547,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3705,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3727,12 +3591,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3749,12 +3613,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3771,12 +3635,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3793,12 +3657,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3815,12 +3679,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3837,12 +3701,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3859,12 +3723,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3881,12 +3745,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3895,776 +3759,6 @@
         </is>
       </c>
       <c r="D119" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -4713,7 +3807,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -4733,7 +3827,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">

--- a/ttl_long/AdHoc_Net_13.xlsx
+++ b/ttl_long/AdHoc_Net_13.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>83</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>341</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>206</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>204</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>205</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>278</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>115</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>212</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>263</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>205</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>263</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>82</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>341</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>372</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>367</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>570</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>151</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>520</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>467</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>563</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>150</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>577</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>586</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>803</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>230</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>701</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>283</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>734</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>850</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>234</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>805</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>294</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>852</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>925</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>203</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1013</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>346</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1026</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1187</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1152</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>279</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1111</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1191</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>148</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1270</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>343</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1246</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1330</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>187</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1356</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>307</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1388</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1576</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1497</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>346</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1490</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1690</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>275</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1587</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1413,12 +1413,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1501,12 +1501,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1677,7 +1677,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1875,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2117,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2183,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2249,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2579,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2777,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2887,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2953,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2975,7 +2975,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3019,12 +3019,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3063,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3107,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3151,12 +3151,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3217,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3239,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3283,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3503,12 +3503,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3569,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3635,12 +3635,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3671,94 +3671,6 @@
         </is>
       </c>
       <c r="D115" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3797,7 +3709,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -3807,7 +3719,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
